--- a/output/graficos_dimensiones/comunal_d_env_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:18</t>
+    <t xml:space="preserve">2026-09-10 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:32</t>
+    <t xml:space="preserve">2026-09-12 22:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:44</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>150.77</v>
+        <v>158.06</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>104.59</v>
+        <v>112.12</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>97.78</v>
+        <v>102.33</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>85.81</v>
+        <v>91.7</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:12</t>
+    <t xml:space="preserve">2026-10-02 16:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:10</t>
+    <t xml:space="preserve">2026-10-05 16:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
